--- a/artfynd/A 19717-2022 artfynd.xlsx
+++ b/artfynd/A 19717-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19717-2022 artfynd.xlsx
+++ b/artfynd/A 19717-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6917554</v>
+        <v>6917615</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Aspåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476784.3191801924</v>
+        <v>476818</v>
       </c>
       <c r="R2" t="n">
-        <v>6669458.763680637</v>
+        <v>6669403</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +745,9 @@
           <t>2013-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +771,398 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6917554</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Södra Aspåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>476784</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6669459</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-08-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-08-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6917617</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Södra Aspåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>476818</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6669403</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2013-08-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2013-08-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6917618</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80367</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Södra Aspåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>476818</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6669403</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2013-08-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2013-08-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6917544</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Södra Aspåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476818</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6669403</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-08-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-08-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
